--- a/Action-敵追加中-/Data/CSV/Stage/Stage.xlsx
+++ b/Action-敵追加中-/Data/CSV/Stage/Stage.xlsx
@@ -1,25 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Documents\GitHub\GameProject\Action\Data\CSV\Stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action-敵追加中-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A01B760-C1D4-44F5-AAB6-54603E591E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{96B7F007-ABCC-40B3-B33F-0521BEB77628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{62A58253-9505-4C17-A0D0-B4C12E04E8CC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stage" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -29,19 +26,160 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="游ゴシック Light"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
@@ -55,15 +193,188 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -71,9 +382,239 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -82,8 +623,49 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - アクセント 1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - アクセント 6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - アクセント 6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - アクセント 6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="アクセント 1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="アクセント 2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="アクセント 3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="アクセント 4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="アクセント 5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="アクセント 6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="タイトル" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="チェック セル" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="どちらでもない" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="メモ" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="リンク セル" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="悪い" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="計算" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="警告文" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="見出し 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="見出し 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="見出し 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="見出し 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="集計" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="出力" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="説明文" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="入力" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="良い" xfId="6" builtinId="26" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -394,14 +976,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{592BFE65-1919-4E86-A258-49B12076C0A7}">
-  <dimension ref="A1:P100"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P99"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="16" width="5.58203125" customWidth="1"/>
+    <col min="1" max="16" width="5.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1">
         <v>0</v>
       </c>
@@ -409,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="C1">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="D1">
         <v>0</v>
@@ -421,17 +1003,17 @@
         <v>0</v>
       </c>
       <c r="G1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H1">
         <v>1</v>
       </c>
       <c r="I1">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="J1">
         <f>G1*20</f>
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="K1">
         <f t="shared" ref="K1:L1" si="0">H1*20</f>
@@ -439,7 +1021,7 @@
       </c>
       <c r="L1">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>420</v>
       </c>
       <c r="M1">
         <v>0</v>
@@ -454,15 +1036,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>-620</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -474,101 +1056,101 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="J2">
-        <f t="shared" ref="J2" si="1">G2*20</f>
+        <f t="shared" ref="J2:J64" si="1">G2*20</f>
+        <v>200</v>
+      </c>
+      <c r="K2">
+        <f t="shared" ref="K2:K64" si="2">H2*20</f>
+        <v>20</v>
+      </c>
+      <c r="L2">
+        <f t="shared" ref="L2:L64" si="3">I2*20</f>
+        <v>420</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3">
+        <v>40</v>
+      </c>
+      <c r="C3">
+        <v>-940</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>10</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>11</v>
+      </c>
+      <c r="J3">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="K3">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="L3">
+        <f t="shared" si="3"/>
+        <v>220</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4">
         <v>60</v>
       </c>
-      <c r="K2">
-        <f t="shared" ref="K2" si="2">H2*20</f>
-        <v>20</v>
-      </c>
-      <c r="L2">
-        <f t="shared" ref="L2" si="3">I2*20</f>
-        <v>20</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
-        <v>0</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>-20</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <f>G3*20</f>
-        <v>60</v>
-      </c>
-      <c r="K3">
-        <f t="shared" ref="K3:K6" si="4">H3*20</f>
-        <v>20</v>
-      </c>
-      <c r="L3">
-        <f t="shared" ref="L3:L6" si="5">I3*20</f>
-        <v>20</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4">
-        <v>0</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
       <c r="C4">
-        <v>-40</v>
+        <v>-1150</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -580,25 +1162,25 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <f t="shared" ref="J4:J6" si="6">G4*20</f>
-        <v>60</v>
+        <f t="shared" ref="J4" si="4">G4*20</f>
+        <v>200</v>
       </c>
       <c r="K4">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="K4" si="5">H4*20</f>
         <v>20</v>
       </c>
       <c r="L4">
-        <f t="shared" si="5"/>
-        <v>20</v>
+        <f t="shared" ref="L4" si="6">I4*20</f>
+        <v>200</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -613,7 +1195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>0</v>
       </c>
@@ -621,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>-60</v>
+        <v>-1460</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -633,25 +1215,25 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="J5">
-        <f t="shared" si="6"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>200</v>
       </c>
       <c r="K5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L5">
-        <f t="shared" si="5"/>
-        <v>20</v>
+        <f t="shared" si="3"/>
+        <v>420</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -666,15 +1248,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C6">
-        <v>-80</v>
+        <v>-1280</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -689,22 +1271,22 @@
         <v>3</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="K6">
-        <f t="shared" si="4"/>
-        <v>20</v>
+        <f t="shared" si="2"/>
+        <v>40</v>
       </c>
       <c r="L6">
-        <f t="shared" si="5"/>
-        <v>20</v>
+        <f t="shared" si="3"/>
+        <v>60</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -719,15 +1301,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7">
-        <v>0</v>
+        <v>-70</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C7">
-        <v>-100</v>
+        <v>-1280</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -742,22 +1324,22 @@
         <v>3</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <f t="shared" ref="J7" si="7">G7*20</f>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="K7">
-        <f t="shared" ref="K7" si="8">H7*20</f>
-        <v>20</v>
+        <f t="shared" si="2"/>
+        <v>40</v>
       </c>
       <c r="L7">
-        <f t="shared" ref="L7" si="9">I7*20</f>
-        <v>20</v>
+        <f t="shared" si="3"/>
+        <v>60</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -772,15 +1354,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A8">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B8">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="C8">
-        <v>-140</v>
+        <v>-1280</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -792,24 +1374,24 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I8">
         <v>3</v>
       </c>
       <c r="J8">
-        <f t="shared" ref="J8:J9" si="10">G8*20</f>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>80</v>
       </c>
       <c r="K8">
-        <f t="shared" ref="K8" si="11">H8*20</f>
-        <v>20</v>
+        <f t="shared" si="2"/>
+        <v>80</v>
       </c>
       <c r="L8">
-        <f t="shared" ref="L8" si="12">I8*20</f>
+        <f t="shared" si="3"/>
         <v>60</v>
       </c>
       <c r="M8">
@@ -825,15 +1407,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>0</v>
       </c>
       <c r="B9">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="C9">
-        <v>-140</v>
+        <v>-1370</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -845,325 +1427,325 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9">
+        <v>4</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10">
+        <v>60</v>
+      </c>
+      <c r="C10">
+        <v>-1470</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>4</v>
+      </c>
+      <c r="H10">
         <v>3</v>
       </c>
-      <c r="J9">
-        <f t="shared" si="10"/>
-        <v>20</v>
-      </c>
-      <c r="K9">
-        <f t="shared" ref="K9:K12" si="13">H9*20</f>
-        <v>20</v>
-      </c>
-      <c r="L9">
-        <f t="shared" ref="L9:L12" si="14">I9*20</f>
+      <c r="I10">
+        <v>4</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10">
-        <v>-20</v>
-      </c>
-      <c r="B10">
-        <v>20</v>
-      </c>
-      <c r="C10">
-        <v>-140</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10">
+      <c r="L10">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11">
+        <v>80</v>
+      </c>
+      <c r="C11">
+        <v>-1590</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>4</v>
+      </c>
+      <c r="H11">
+        <v>4</v>
+      </c>
+      <c r="I11">
+        <v>4</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="2"/>
+        <v>80</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12">
+        <v>80</v>
+      </c>
+      <c r="C12">
+        <v>-1680</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>10</v>
+      </c>
+      <c r="H12">
+        <v>4</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="2"/>
+        <v>80</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13">
+        <v>80</v>
+      </c>
+      <c r="C13">
+        <v>-1900</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>10</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>21</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="3"/>
+        <v>420</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>0</v>
+      </c>
+      <c r="B14">
+        <v>100</v>
+      </c>
+      <c r="C14">
+        <v>-2360</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>25</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>25</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="3"/>
+        <v>500</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15">
+        <v>100</v>
+      </c>
+      <c r="C15">
+        <v>-2660</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
         <v>3</v>
-      </c>
-      <c r="J10">
-        <f t="shared" ref="J10:J12" si="15">G10*20</f>
-        <v>20</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="13"/>
-        <v>20</v>
-      </c>
-      <c r="L10">
-        <f t="shared" si="14"/>
-        <v>60</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11">
-        <v>-40</v>
-      </c>
-      <c r="B11">
-        <v>20</v>
-      </c>
-      <c r="C11">
-        <v>-140</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11">
-        <v>3</v>
-      </c>
-      <c r="J11">
-        <f t="shared" si="15"/>
-        <v>20</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="13"/>
-        <v>20</v>
-      </c>
-      <c r="L11">
-        <f t="shared" si="14"/>
-        <v>60</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12">
-        <v>-60</v>
-      </c>
-      <c r="B12">
-        <v>20</v>
-      </c>
-      <c r="C12">
-        <v>-140</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="I12">
-        <v>3</v>
-      </c>
-      <c r="J12">
-        <f t="shared" si="15"/>
-        <v>20</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="13"/>
-        <v>20</v>
-      </c>
-      <c r="L12">
-        <f t="shared" si="14"/>
-        <v>60</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13">
-        <v>-80</v>
-      </c>
-      <c r="B13">
-        <v>20</v>
-      </c>
-      <c r="C13">
-        <v>-140</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13">
-        <v>3</v>
-      </c>
-      <c r="J13">
-        <f t="shared" ref="J13:J15" si="16">G13*20</f>
-        <v>20</v>
-      </c>
-      <c r="K13">
-        <f t="shared" ref="K13:K16" si="17">H13*20</f>
-        <v>20</v>
-      </c>
-      <c r="L13">
-        <f t="shared" ref="L13:L16" si="18">I13*20</f>
-        <v>60</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14">
-        <v>-100</v>
-      </c>
-      <c r="B14">
-        <v>20</v>
-      </c>
-      <c r="C14">
-        <v>-140</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="I14">
-        <v>3</v>
-      </c>
-      <c r="J14">
-        <f t="shared" si="16"/>
-        <v>20</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="17"/>
-        <v>20</v>
-      </c>
-      <c r="L14">
-        <f t="shared" si="18"/>
-        <v>60</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15">
-        <v>-120</v>
-      </c>
-      <c r="B15">
-        <v>20</v>
-      </c>
-      <c r="C15">
-        <v>-140</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -1172,39 +1754,39 @@
         <v>3</v>
       </c>
       <c r="J15">
-        <f t="shared" si="16"/>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>60</v>
       </c>
       <c r="K15">
-        <f t="shared" si="17"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L15">
-        <f t="shared" si="18"/>
+        <f t="shared" si="3"/>
         <v>60</v>
       </c>
       <c r="M15">
         <v>0</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>-2640</v>
       </c>
       <c r="P15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A16">
-        <v>-140</v>
+        <v>0</v>
       </c>
       <c r="B16">
-        <v>20</v>
+        <v>-1000</v>
       </c>
       <c r="C16">
-        <v>-140</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1222,19 +1804,19 @@
         <v>1</v>
       </c>
       <c r="I16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <f t="shared" ref="J16:J18" si="19">G16*20</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K16">
-        <f t="shared" si="17"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L16">
-        <f t="shared" si="18"/>
-        <v>60</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="M16">
         <v>0</v>
@@ -1249,15 +1831,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A17">
-        <v>-160</v>
+        <v>0</v>
       </c>
       <c r="B17">
-        <v>20</v>
+        <v>-1000</v>
       </c>
       <c r="C17">
-        <v>-140</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1275,19 +1857,19 @@
         <v>1</v>
       </c>
       <c r="I17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K17">
-        <f t="shared" ref="K17:K20" si="20">H17*20</f>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L17">
-        <f t="shared" ref="L17:L20" si="21">I17*20</f>
-        <v>60</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -1302,15 +1884,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A18">
-        <v>-180</v>
+        <v>0</v>
       </c>
       <c r="B18">
-        <v>20</v>
+        <v>-1000</v>
       </c>
       <c r="C18">
-        <v>-140</v>
+        <v>0</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1328,19 +1910,19 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <f t="shared" si="19"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K18">
-        <f t="shared" si="20"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L18">
-        <f t="shared" si="21"/>
-        <v>60</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -1355,15 +1937,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A19">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="B19">
-        <v>20</v>
+        <v>-1000</v>
       </c>
       <c r="C19">
-        <v>-140</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1381,19 +1963,19 @@
         <v>1</v>
       </c>
       <c r="I19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <f t="shared" ref="J19:J21" si="22">G19*20</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K19">
-        <f t="shared" si="20"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L19">
-        <f t="shared" si="21"/>
-        <v>60</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="M19">
         <v>0</v>
@@ -1408,15 +1990,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A20">
-        <v>-180</v>
+        <v>0</v>
       </c>
       <c r="B20">
-        <v>20</v>
+        <v>-1000</v>
       </c>
       <c r="C20">
-        <v>-180</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -1428,7 +2010,7 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -1437,15 +2019,15 @@
         <v>1</v>
       </c>
       <c r="J20">
-        <f t="shared" si="22"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K20">
-        <f t="shared" si="20"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L20">
-        <f t="shared" si="21"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M20">
@@ -1461,15 +2043,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A21">
-        <v>-180</v>
+        <v>0</v>
       </c>
       <c r="B21">
-        <v>20</v>
+        <v>-1000</v>
       </c>
       <c r="C21">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1481,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -1490,15 +2072,15 @@
         <v>1</v>
       </c>
       <c r="J21">
-        <f t="shared" si="22"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K21">
-        <f t="shared" ref="K21:K24" si="23">H21*20</f>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L21">
-        <f t="shared" ref="L21:L24" si="24">I21*20</f>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M21">
@@ -1514,15 +2096,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A22">
-        <v>-180</v>
+        <v>0</v>
       </c>
       <c r="B22">
-        <v>20</v>
+        <v>-1000</v>
       </c>
       <c r="C22">
-        <v>-220</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1534,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -1543,15 +2125,15 @@
         <v>1</v>
       </c>
       <c r="J22">
-        <f t="shared" ref="J22:J24" si="25">G22*20</f>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K22">
-        <f t="shared" si="23"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L22">
-        <f t="shared" si="24"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M22">
@@ -1567,15 +2149,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A23">
-        <v>-180</v>
+        <v>0</v>
       </c>
       <c r="B23">
-        <v>20</v>
+        <v>-1000</v>
       </c>
       <c r="C23">
-        <v>-240</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -1587,7 +2169,7 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -1596,15 +2178,15 @@
         <v>1</v>
       </c>
       <c r="J23">
-        <f t="shared" si="25"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M23">
@@ -1620,15 +2202,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A24">
-        <v>-180</v>
+        <v>0</v>
       </c>
       <c r="B24">
-        <v>20</v>
+        <v>-1000</v>
       </c>
       <c r="C24">
-        <v>-260</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1640,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -1649,15 +2231,15 @@
         <v>1</v>
       </c>
       <c r="J24">
-        <f t="shared" si="25"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K24">
-        <f t="shared" si="23"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L24">
-        <f t="shared" si="24"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M24">
@@ -1673,15 +2255,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A25">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="B25">
-        <v>20</v>
+        <v>-1000</v>
       </c>
       <c r="C25">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -1699,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="I25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <f t="shared" ref="J25:J27" si="26">G25*20</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K25">
-        <f t="shared" ref="K25:K28" si="27">H25*20</f>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L25">
-        <f t="shared" ref="L25:L28" si="28">I25*20</f>
-        <v>60</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="M25">
         <v>0</v>
@@ -1726,15 +2308,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A26">
-        <v>-180</v>
+        <v>0</v>
       </c>
       <c r="B26">
-        <v>20</v>
+        <v>-1000</v>
       </c>
       <c r="C26">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -1752,19 +2334,19 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J26">
-        <f t="shared" si="26"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K26">
-        <f t="shared" si="27"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L26">
-        <f t="shared" si="28"/>
-        <v>60</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="M26">
         <v>0</v>
@@ -1779,15 +2361,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A27">
-        <v>-160</v>
+        <v>0</v>
       </c>
       <c r="B27">
-        <v>20</v>
+        <v>-1000</v>
       </c>
       <c r="C27">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -1805,19 +2387,19 @@
         <v>1</v>
       </c>
       <c r="I27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K27">
-        <f t="shared" si="27"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L27">
-        <f t="shared" si="28"/>
-        <v>60</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -1832,15 +2414,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A28">
-        <v>-140</v>
+        <v>0</v>
       </c>
       <c r="B28">
-        <v>20</v>
+        <v>-1000</v>
       </c>
       <c r="C28">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -1858,19 +2440,19 @@
         <v>1</v>
       </c>
       <c r="I28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J28">
-        <f t="shared" ref="J28:J30" si="29">G28*20</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K28">
-        <f t="shared" si="27"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L28">
-        <f t="shared" si="28"/>
-        <v>60</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="M28">
         <v>0</v>
@@ -1885,15 +2467,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A29">
-        <v>-120</v>
+        <v>0</v>
       </c>
       <c r="B29">
-        <v>20</v>
+        <v>-1000</v>
       </c>
       <c r="C29">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1911,19 +2493,19 @@
         <v>1</v>
       </c>
       <c r="I29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J29">
-        <f t="shared" si="29"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K29">
-        <f t="shared" ref="K29:K32" si="30">H29*20</f>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L29">
-        <f t="shared" ref="L29:L32" si="31">I29*20</f>
-        <v>60</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="M29">
         <v>0</v>
@@ -1938,15 +2520,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A30">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="B30">
-        <v>20</v>
+        <v>-1000</v>
       </c>
       <c r="C30">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1964,19 +2546,19 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J30">
-        <f t="shared" si="29"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K30">
-        <f t="shared" si="30"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L30">
-        <f t="shared" si="31"/>
-        <v>60</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="M30">
         <v>0</v>
@@ -1991,15 +2573,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A31">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="B31">
-        <v>40</v>
+        <v>-1000</v>
       </c>
       <c r="C31">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -2017,19 +2599,19 @@
         <v>1</v>
       </c>
       <c r="I31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J31">
-        <f t="shared" ref="J31:J33" si="32">G31*20</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K31">
-        <f t="shared" si="30"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L31">
-        <f t="shared" si="31"/>
-        <v>60</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="M31">
         <v>0</v>
@@ -2044,15 +2626,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A32">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="B32">
-        <v>40</v>
+        <v>-1000</v>
       </c>
       <c r="C32">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -2070,19 +2652,19 @@
         <v>1</v>
       </c>
       <c r="I32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J32">
-        <f t="shared" si="32"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K32">
-        <f t="shared" si="30"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L32">
-        <f t="shared" si="31"/>
-        <v>60</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="M32">
         <v>0</v>
@@ -2097,15 +2679,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A33">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="B33">
-        <v>40</v>
+        <v>-1000</v>
       </c>
       <c r="C33">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -2123,19 +2705,19 @@
         <v>1</v>
       </c>
       <c r="I33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J33">
-        <f t="shared" si="32"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K33">
-        <f t="shared" ref="K33:K36" si="33">H33*20</f>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L33">
-        <f t="shared" ref="L33:L36" si="34">I33*20</f>
-        <v>60</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="M33">
         <v>0</v>
@@ -2150,15 +2732,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A34">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B34">
-        <v>60</v>
+        <v>-1000</v>
       </c>
       <c r="C34">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -2176,19 +2758,19 @@
         <v>1</v>
       </c>
       <c r="I34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J34">
-        <f t="shared" ref="J34:J36" si="35">G34*20</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K34">
-        <f t="shared" si="33"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L34">
-        <f t="shared" si="34"/>
-        <v>60</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="M34">
         <v>0</v>
@@ -2203,15 +2785,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A35">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="B35">
-        <v>60</v>
+        <v>-1000</v>
       </c>
       <c r="C35">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -2229,19 +2811,19 @@
         <v>1</v>
       </c>
       <c r="I35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J35">
-        <f t="shared" si="35"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K35">
-        <f t="shared" si="33"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L35">
-        <f t="shared" si="34"/>
-        <v>60</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="M35">
         <v>0</v>
@@ -2256,15 +2838,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A36">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B36">
-        <v>60</v>
+        <v>-1000</v>
       </c>
       <c r="C36">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -2282,19 +2864,19 @@
         <v>1</v>
       </c>
       <c r="I36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J36">
-        <f t="shared" si="35"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K36">
-        <f t="shared" si="33"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L36">
-        <f t="shared" si="34"/>
-        <v>60</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -2309,15 +2891,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A37">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="B37">
-        <v>80</v>
+        <v>-1000</v>
       </c>
       <c r="C37">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -2335,19 +2917,19 @@
         <v>1</v>
       </c>
       <c r="I37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J37">
-        <f t="shared" ref="J37:J100" si="36">G37*20</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K37">
-        <f t="shared" ref="K37:K100" si="37">H37*20</f>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L37">
-        <f t="shared" ref="L37:L100" si="38">I37*20</f>
-        <v>60</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="M37">
         <v>0</v>
@@ -2362,15 +2944,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A38">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="B38">
-        <v>80</v>
+        <v>-1000</v>
       </c>
       <c r="C38">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2388,19 +2970,19 @@
         <v>1</v>
       </c>
       <c r="I38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J38">
-        <f t="shared" si="36"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K38">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L38">
-        <f t="shared" si="38"/>
-        <v>60</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="M38">
         <v>0</v>
@@ -2415,15 +2997,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A39">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="B39">
-        <v>80</v>
+        <v>-1000</v>
       </c>
       <c r="C39">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -2441,19 +3023,19 @@
         <v>1</v>
       </c>
       <c r="I39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J39">
-        <f t="shared" si="36"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K39">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L39">
-        <f t="shared" si="38"/>
-        <v>60</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="M39">
         <v>0</v>
@@ -2468,15 +3050,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A40">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="B40">
-        <v>100</v>
+        <v>-1000</v>
       </c>
       <c r="C40">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -2494,19 +3076,19 @@
         <v>1</v>
       </c>
       <c r="I40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J40">
-        <f t="shared" si="36"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K40">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L40">
-        <f t="shared" si="38"/>
-        <v>60</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="M40">
         <v>0</v>
@@ -2521,15 +3103,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A41">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="B41">
-        <v>100</v>
+        <v>-1000</v>
       </c>
       <c r="C41">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -2547,19 +3129,19 @@
         <v>1</v>
       </c>
       <c r="I41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J41">
-        <f t="shared" si="36"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K41">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L41">
-        <f t="shared" si="38"/>
-        <v>60</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="M41">
         <v>0</v>
@@ -2574,15 +3156,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A42">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="B42">
-        <v>100</v>
+        <v>-1000</v>
       </c>
       <c r="C42">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -2600,19 +3182,19 @@
         <v>1</v>
       </c>
       <c r="I42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J42">
-        <f t="shared" si="36"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K42">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L42">
-        <f t="shared" si="38"/>
-        <v>60</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="M42">
         <v>0</v>
@@ -2627,15 +3209,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A43">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="B43">
-        <v>100</v>
+        <v>-1000</v>
       </c>
       <c r="C43">
-        <v>-320</v>
+        <v>0</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -2647,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="G43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H43">
         <v>1</v>
@@ -2656,15 +3238,15 @@
         <v>1</v>
       </c>
       <c r="J43">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K43">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L43">
-        <f t="shared" si="38"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M43">
@@ -2680,15 +3262,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A44">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="B44">
-        <v>100</v>
+        <v>-1000</v>
       </c>
       <c r="C44">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -2700,7 +3282,7 @@
         <v>0</v>
       </c>
       <c r="G44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -2709,15 +3291,15 @@
         <v>1</v>
       </c>
       <c r="J44">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K44">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L44">
-        <f t="shared" si="38"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M44">
@@ -2733,15 +3315,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A45">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="B45">
-        <v>100</v>
+        <v>-1000</v>
       </c>
       <c r="C45">
-        <v>-280</v>
+        <v>0</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2753,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -2762,15 +3344,15 @@
         <v>1</v>
       </c>
       <c r="J45">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K45">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L45">
-        <f t="shared" si="38"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M45">
@@ -2786,15 +3368,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A46">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="B46">
-        <v>100</v>
+        <v>-1000</v>
       </c>
       <c r="C46">
-        <v>-260</v>
+        <v>0</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2806,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -2815,15 +3397,15 @@
         <v>1</v>
       </c>
       <c r="J46">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K46">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L46">
-        <f t="shared" si="38"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M46">
@@ -2839,15 +3421,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A47">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="B47">
-        <v>100</v>
+        <v>-1000</v>
       </c>
       <c r="C47">
-        <v>-240</v>
+        <v>0</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2859,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="G47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H47">
         <v>1</v>
@@ -2868,15 +3450,15 @@
         <v>1</v>
       </c>
       <c r="J47">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K47">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L47">
-        <f t="shared" si="38"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M47">
@@ -2892,15 +3474,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A48">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="B48">
-        <v>100</v>
+        <v>-1000</v>
       </c>
       <c r="C48">
-        <v>-220</v>
+        <v>0</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2912,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="G48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -2921,15 +3503,15 @@
         <v>1</v>
       </c>
       <c r="J48">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K48">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L48">
-        <f t="shared" si="38"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M48">
@@ -2945,15 +3527,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A49">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="B49">
-        <v>100</v>
+        <v>-1000</v>
       </c>
       <c r="C49">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2965,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H49">
         <v>1</v>
@@ -2974,15 +3556,15 @@
         <v>1</v>
       </c>
       <c r="J49">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K49">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L49">
-        <f t="shared" si="38"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M49">
@@ -2998,15 +3580,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A50">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="B50">
-        <v>100</v>
+        <v>-1000</v>
       </c>
       <c r="C50">
-        <v>-180</v>
+        <v>0</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -3018,7 +3600,7 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H50">
         <v>1</v>
@@ -3027,15 +3609,15 @@
         <v>1</v>
       </c>
       <c r="J50">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K50">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L50">
-        <f t="shared" si="38"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M50">
@@ -3051,15 +3633,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A51">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="B51">
-        <v>100</v>
+        <v>-1000</v>
       </c>
       <c r="C51">
-        <v>-160</v>
+        <v>0</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -3071,7 +3653,7 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H51">
         <v>1</v>
@@ -3080,15 +3662,15 @@
         <v>1</v>
       </c>
       <c r="J51">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K51">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L51">
-        <f t="shared" si="38"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M51">
@@ -3104,15 +3686,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A52">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="B52">
-        <v>120</v>
+        <v>-1000</v>
       </c>
       <c r="C52">
-        <v>-120</v>
+        <v>0</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -3124,7 +3706,7 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -3133,15 +3715,15 @@
         <v>1</v>
       </c>
       <c r="J52">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K52">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L52">
-        <f t="shared" si="38"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M52">
@@ -3157,15 +3739,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A53">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="B53">
-        <v>120</v>
+        <v>-1000</v>
       </c>
       <c r="C53">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -3177,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="G53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H53">
         <v>1</v>
@@ -3186,15 +3768,15 @@
         <v>1</v>
       </c>
       <c r="J53">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K53">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L53">
-        <f t="shared" si="38"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M53">
@@ -3210,15 +3792,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A54">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="B54">
-        <v>120</v>
+        <v>-1000</v>
       </c>
       <c r="C54">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -3230,7 +3812,7 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H54">
         <v>1</v>
@@ -3239,15 +3821,15 @@
         <v>1</v>
       </c>
       <c r="J54">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K54">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L54">
-        <f t="shared" si="38"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M54">
@@ -3263,15 +3845,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A55">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="B55">
-        <v>140</v>
+        <v>-1000</v>
       </c>
       <c r="C55">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -3283,7 +3865,7 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H55">
         <v>1</v>
@@ -3292,15 +3874,15 @@
         <v>1</v>
       </c>
       <c r="J55">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K55">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L55">
-        <f t="shared" si="38"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M55">
@@ -3316,15 +3898,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A56">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="B56">
-        <v>140</v>
+        <v>-1000</v>
       </c>
       <c r="C56">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -3336,7 +3918,7 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H56">
         <v>1</v>
@@ -3345,15 +3927,15 @@
         <v>1</v>
       </c>
       <c r="J56">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K56">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L56">
-        <f t="shared" si="38"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M56">
@@ -3369,12 +3951,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A57">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="B57">
-        <v>140</v>
+        <v>-1000</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -3389,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H57">
         <v>1</v>
@@ -3398,15 +3980,15 @@
         <v>1</v>
       </c>
       <c r="J57">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K57">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L57">
-        <f t="shared" si="38"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M57">
@@ -3422,15 +4004,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A58">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="B58">
-        <v>160</v>
+        <v>-1000</v>
       </c>
       <c r="C58">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -3442,7 +4024,7 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H58">
         <v>1</v>
@@ -3451,15 +4033,15 @@
         <v>1</v>
       </c>
       <c r="J58">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K58">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L58">
-        <f t="shared" si="38"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M58">
@@ -3475,15 +4057,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A59">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="B59">
-        <v>160</v>
+        <v>-1000</v>
       </c>
       <c r="C59">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -3495,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="G59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H59">
         <v>1</v>
@@ -3504,15 +4086,15 @@
         <v>1</v>
       </c>
       <c r="J59">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K59">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L59">
-        <f t="shared" si="38"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M59">
@@ -3528,15 +4110,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A60">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="B60">
-        <v>160</v>
+        <v>-1000</v>
       </c>
       <c r="C60">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -3548,7 +4130,7 @@
         <v>0</v>
       </c>
       <c r="G60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H60">
         <v>1</v>
@@ -3557,15 +4139,15 @@
         <v>1</v>
       </c>
       <c r="J60">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K60">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L60">
-        <f t="shared" si="38"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M60">
@@ -3581,15 +4163,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A61">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="B61">
-        <v>180</v>
+        <v>-1000</v>
       </c>
       <c r="C61">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -3601,7 +4183,7 @@
         <v>0</v>
       </c>
       <c r="G61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H61">
         <v>1</v>
@@ -3610,15 +4192,15 @@
         <v>1</v>
       </c>
       <c r="J61">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K61">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L61">
-        <f t="shared" si="38"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M61">
@@ -3634,15 +4216,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A62">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="B62">
-        <v>180</v>
+        <v>-1000</v>
       </c>
       <c r="C62">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -3654,7 +4236,7 @@
         <v>0</v>
       </c>
       <c r="G62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H62">
         <v>1</v>
@@ -3663,15 +4245,15 @@
         <v>1</v>
       </c>
       <c r="J62">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K62">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L62">
-        <f t="shared" si="38"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M62">
@@ -3687,15 +4269,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A63">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="B63">
-        <v>180</v>
+        <v>-1000</v>
       </c>
       <c r="C63">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -3707,7 +4289,7 @@
         <v>0</v>
       </c>
       <c r="G63">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H63">
         <v>1</v>
@@ -3716,15 +4298,15 @@
         <v>1</v>
       </c>
       <c r="J63">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K63">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L63">
-        <f t="shared" si="38"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="M63">
@@ -3740,15 +4322,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A64">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="B64">
-        <v>180</v>
+        <v>-1000</v>
       </c>
       <c r="C64">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -3760,48 +4342,48 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H64">
         <v>1</v>
       </c>
       <c r="I64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J64">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="K64">
-        <f t="shared" si="37"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L64">
-        <f t="shared" si="38"/>
-        <v>60</v>
+        <f t="shared" si="3"/>
+        <v>20</v>
       </c>
       <c r="M64">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="N64">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="O64">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="P64">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A65">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="B65">
-        <v>280</v>
+        <v>-1000</v>
       </c>
       <c r="C65">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -3813,25 +4395,25 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H65">
         <v>1</v>
       </c>
       <c r="I65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J65">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" ref="J65:J99" si="7">G65*20</f>
+        <v>20</v>
       </c>
       <c r="K65">
-        <f t="shared" si="37"/>
+        <f t="shared" ref="K65:K99" si="8">H65*20</f>
         <v>20</v>
       </c>
       <c r="L65">
-        <f t="shared" si="38"/>
-        <v>60</v>
+        <f t="shared" ref="L65:L99" si="9">I65*20</f>
+        <v>20</v>
       </c>
       <c r="M65">
         <v>0</v>
@@ -3846,15 +4428,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A66">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="B66">
-        <v>280</v>
+        <v>-1000</v>
       </c>
       <c r="C66">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -3866,48 +4448,48 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H66">
         <v>1</v>
       </c>
       <c r="I66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J66">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="K66">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L66">
-        <f t="shared" si="38"/>
-        <v>60</v>
+        <f t="shared" si="9"/>
+        <v>20</v>
       </c>
       <c r="M66">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="N66">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="O66">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="P66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A67">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="B67">
-        <v>280</v>
+        <v>-1000</v>
       </c>
       <c r="C67">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -3925,19 +4507,19 @@
         <v>1</v>
       </c>
       <c r="I67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J67">
-        <f t="shared" si="36"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="K67">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L67">
-        <f t="shared" si="38"/>
-        <v>60</v>
+        <f t="shared" si="9"/>
+        <v>20</v>
       </c>
       <c r="M67">
         <v>0</v>
@@ -3952,15 +4534,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A68">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="B68">
-        <v>280</v>
+        <v>-1000</v>
       </c>
       <c r="C68">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -3978,19 +4560,19 @@
         <v>1</v>
       </c>
       <c r="I68">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J68">
-        <f t="shared" si="36"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="K68">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L68">
-        <f t="shared" si="38"/>
-        <v>60</v>
+        <f t="shared" si="9"/>
+        <v>20</v>
       </c>
       <c r="M68">
         <v>0</v>
@@ -4005,15 +4587,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A69">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="B69">
-        <v>280</v>
+        <v>-1000</v>
       </c>
       <c r="C69">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -4031,19 +4613,19 @@
         <v>1</v>
       </c>
       <c r="I69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J69">
-        <f t="shared" si="36"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="K69">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L69">
-        <f t="shared" si="38"/>
-        <v>60</v>
+        <f t="shared" si="9"/>
+        <v>20</v>
       </c>
       <c r="M69">
         <v>0</v>
@@ -4058,15 +4640,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A70">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="B70">
-        <v>280</v>
+        <v>-1000</v>
       </c>
       <c r="C70">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -4078,48 +4660,48 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H70">
         <v>1</v>
       </c>
       <c r="I70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J70">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="K70">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L70">
-        <f t="shared" si="38"/>
-        <v>60</v>
+        <f t="shared" si="9"/>
+        <v>20</v>
       </c>
       <c r="M70">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N70">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="O70">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A71">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="B71">
-        <v>480</v>
+        <v>-1000</v>
       </c>
       <c r="C71">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -4131,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="G71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H71">
         <v>1</v>
@@ -4140,15 +4722,15 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="K71">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L71">
-        <f t="shared" si="38"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="M71">
@@ -4164,15 +4746,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>0</v>
       </c>
       <c r="B72">
-        <v>480</v>
+        <v>-1000</v>
       </c>
       <c r="C72">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -4184,7 +4766,7 @@
         <v>0</v>
       </c>
       <c r="G72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H72">
         <v>1</v>
@@ -4193,15 +4775,15 @@
         <v>1</v>
       </c>
       <c r="J72">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="K72">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L72">
-        <f t="shared" si="38"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="M72">
@@ -4217,15 +4799,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>0</v>
       </c>
       <c r="B73">
-        <v>480</v>
+        <v>-1000</v>
       </c>
       <c r="C73">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -4237,7 +4819,7 @@
         <v>0</v>
       </c>
       <c r="G73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H73">
         <v>1</v>
@@ -4246,15 +4828,15 @@
         <v>1</v>
       </c>
       <c r="J73">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="K73">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L73">
-        <f t="shared" si="38"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="M73">
@@ -4270,15 +4852,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A74">
         <v>0</v>
       </c>
       <c r="B74">
-        <v>480</v>
+        <v>-1000</v>
       </c>
       <c r="C74">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -4290,7 +4872,7 @@
         <v>0</v>
       </c>
       <c r="G74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H74">
         <v>1</v>
@@ -4299,15 +4881,15 @@
         <v>1</v>
       </c>
       <c r="J74">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="K74">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L74">
-        <f t="shared" si="38"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="M74">
@@ -4323,15 +4905,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A75">
         <v>0</v>
       </c>
       <c r="B75">
-        <v>490</v>
+        <v>-1000</v>
       </c>
       <c r="C75">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -4343,7 +4925,7 @@
         <v>0</v>
       </c>
       <c r="G75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H75">
         <v>1</v>
@@ -4352,15 +4934,15 @@
         <v>1</v>
       </c>
       <c r="J75">
-        <f t="shared" si="36"/>
-        <v>40</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="K75">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L75">
-        <f t="shared" si="38"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="M75">
@@ -4376,15 +4958,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A76">
         <v>0</v>
       </c>
       <c r="B76">
-        <v>490</v>
+        <v>-1000</v>
       </c>
       <c r="C76">
-        <v>-140</v>
+        <v>0</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -4396,7 +4978,7 @@
         <v>0</v>
       </c>
       <c r="G76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H76">
         <v>1</v>
@@ -4405,15 +4987,15 @@
         <v>1</v>
       </c>
       <c r="J76">
-        <f t="shared" si="36"/>
-        <v>40</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="K76">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L76">
-        <f t="shared" si="38"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="M76">
@@ -4429,15 +5011,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>0</v>
       </c>
       <c r="B77">
-        <v>490</v>
+        <v>-1000</v>
       </c>
       <c r="C77">
-        <v>-180</v>
+        <v>0</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -4449,7 +5031,7 @@
         <v>0</v>
       </c>
       <c r="G77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H77">
         <v>1</v>
@@ -4458,15 +5040,15 @@
         <v>1</v>
       </c>
       <c r="J77">
-        <f t="shared" si="36"/>
-        <v>40</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="K77">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L77">
-        <f t="shared" si="38"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="M77">
@@ -4482,15 +5064,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A78">
         <v>0</v>
       </c>
       <c r="B78">
-        <v>500</v>
+        <v>-1000</v>
       </c>
       <c r="C78">
-        <v>-220</v>
+        <v>0</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -4511,15 +5093,15 @@
         <v>1</v>
       </c>
       <c r="J78">
-        <f t="shared" si="36"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="K78">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L78">
-        <f t="shared" si="38"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="M78">
@@ -4535,15 +5117,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A79">
         <v>0</v>
       </c>
       <c r="B79">
-        <v>500</v>
+        <v>-1000</v>
       </c>
       <c r="C79">
-        <v>-260</v>
+        <v>0</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -4564,15 +5146,15 @@
         <v>1</v>
       </c>
       <c r="J79">
-        <f t="shared" si="36"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="K79">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L79">
-        <f t="shared" si="38"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="M79">
@@ -4588,15 +5170,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A80">
         <v>0</v>
       </c>
       <c r="B80">
-        <v>500</v>
+        <v>-1000</v>
       </c>
       <c r="C80">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -4617,15 +5199,15 @@
         <v>1</v>
       </c>
       <c r="J80">
-        <f t="shared" si="36"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="K80">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L80">
-        <f t="shared" si="38"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="M80">
@@ -4641,15 +5223,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A81">
         <v>0</v>
       </c>
       <c r="B81">
-        <v>520</v>
+        <v>-1000</v>
       </c>
       <c r="C81">
-        <v>-340</v>
+        <v>0</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -4670,15 +5252,15 @@
         <v>1</v>
       </c>
       <c r="J81">
-        <f t="shared" si="36"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="K81">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L81">
-        <f t="shared" si="38"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="M81">
@@ -4694,15 +5276,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A82">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="B82">
-        <v>500</v>
+        <v>-1000</v>
       </c>
       <c r="C82">
-        <v>-420</v>
+        <v>0</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -4714,48 +5296,48 @@
         <v>0</v>
       </c>
       <c r="G82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H82">
         <v>1</v>
       </c>
       <c r="I82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J82">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="K82">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L82">
-        <f t="shared" si="38"/>
-        <v>60</v>
+        <f t="shared" si="9"/>
+        <v>20</v>
       </c>
       <c r="M82">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N82">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="O82">
-        <v>-420</v>
+        <v>0</v>
       </c>
       <c r="P82">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A83">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="B83">
-        <v>800</v>
+        <v>-1000</v>
       </c>
       <c r="C83">
-        <v>-420</v>
+        <v>0</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -4767,48 +5349,48 @@
         <v>0</v>
       </c>
       <c r="G83">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H83">
         <v>1</v>
       </c>
       <c r="I83">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J83">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="K83">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L83">
-        <f t="shared" si="38"/>
-        <v>60</v>
+        <f t="shared" si="9"/>
+        <v>20</v>
       </c>
       <c r="M83">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="N83">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="O83">
-        <v>-420</v>
+        <v>0</v>
       </c>
       <c r="P83">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A84">
         <v>0</v>
       </c>
       <c r="B84">
-        <v>800</v>
+        <v>-1000</v>
       </c>
       <c r="C84">
-        <v>-480</v>
+        <v>0</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -4829,15 +5411,15 @@
         <v>1</v>
       </c>
       <c r="J84">
-        <f t="shared" si="36"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="K84">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L84">
-        <f t="shared" si="38"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="M84">
@@ -4853,15 +5435,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A85">
         <v>0</v>
       </c>
       <c r="B85">
-        <v>700</v>
+        <v>-1000</v>
       </c>
       <c r="C85">
-        <v>-520</v>
+        <v>0</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -4873,48 +5455,48 @@
         <v>0</v>
       </c>
       <c r="G85">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H85">
         <v>1</v>
       </c>
       <c r="I85">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J85">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="K85">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L85">
-        <f t="shared" si="38"/>
-        <v>60</v>
+        <f t="shared" si="9"/>
+        <v>20</v>
       </c>
       <c r="M85">
         <v>0</v>
       </c>
       <c r="N85">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="O85">
-        <v>-1020</v>
+        <v>0</v>
       </c>
       <c r="P85">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A86">
         <v>0</v>
       </c>
       <c r="B86">
-        <v>1200</v>
+        <v>-1000</v>
       </c>
       <c r="C86">
-        <v>-1080</v>
+        <v>0</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -4926,25 +5508,25 @@
         <v>0</v>
       </c>
       <c r="G86">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H86">
         <v>1</v>
       </c>
       <c r="I86">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J86">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="K86">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L86">
-        <f t="shared" si="38"/>
-        <v>60</v>
+        <f t="shared" si="9"/>
+        <v>20</v>
       </c>
       <c r="M86">
         <v>0</v>
@@ -4959,15 +5541,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A87">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B87">
-        <v>1200</v>
+        <v>-1000</v>
       </c>
       <c r="C87">
-        <v>-1080</v>
+        <v>0</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -4979,48 +5561,48 @@
         <v>0</v>
       </c>
       <c r="G87">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H87">
         <v>1</v>
       </c>
       <c r="I87">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J87">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="K87">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L87">
-        <f t="shared" si="38"/>
-        <v>60</v>
+        <f t="shared" si="9"/>
+        <v>20</v>
       </c>
       <c r="M87">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N87">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="O87">
-        <v>-280</v>
+        <v>0</v>
       </c>
       <c r="P87">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A88">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="B88">
-        <v>1200</v>
+        <v>-1000</v>
       </c>
       <c r="C88">
-        <v>-280</v>
+        <v>0</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -5032,45 +5614,45 @@
         <v>0</v>
       </c>
       <c r="G88">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H88">
         <v>1</v>
       </c>
       <c r="I88">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J88">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="K88">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L88">
-        <f t="shared" si="38"/>
-        <v>60</v>
+        <f t="shared" si="9"/>
+        <v>20</v>
       </c>
       <c r="M88">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="N88">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="O88">
-        <v>-1080</v>
+        <v>0</v>
       </c>
       <c r="P88">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A89">
         <v>0</v>
       </c>
       <c r="B89">
-        <v>1000</v>
+        <v>-1000</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -5085,25 +5667,25 @@
         <v>0</v>
       </c>
       <c r="G89">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H89">
         <v>1</v>
       </c>
       <c r="I89">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="J89">
-        <f t="shared" si="36"/>
-        <v>500</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="K89">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L89">
-        <f t="shared" si="38"/>
-        <v>500</v>
+        <f t="shared" si="9"/>
+        <v>20</v>
       </c>
       <c r="M89">
         <v>0</v>
@@ -5118,15 +5700,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A90">
         <v>0</v>
       </c>
       <c r="B90">
-        <v>1000</v>
+        <v>-1000</v>
       </c>
       <c r="C90">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -5138,25 +5720,25 @@
         <v>0</v>
       </c>
       <c r="G90">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H90">
         <v>1</v>
       </c>
       <c r="I90">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J90">
-        <f t="shared" si="36"/>
-        <v>300</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="K90">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L90">
-        <f t="shared" si="38"/>
-        <v>220</v>
+        <f t="shared" si="9"/>
+        <v>20</v>
       </c>
       <c r="M90">
         <v>0</v>
@@ -5171,15 +5753,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A91">
         <v>0</v>
       </c>
       <c r="B91">
-        <v>1140</v>
+        <v>-1000</v>
       </c>
       <c r="C91">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -5191,25 +5773,25 @@
         <v>0</v>
       </c>
       <c r="G91">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H91">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I91">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J91">
-        <f t="shared" si="36"/>
-        <v>300</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="K91">
-        <f t="shared" si="37"/>
-        <v>160</v>
+        <f t="shared" si="8"/>
+        <v>20</v>
       </c>
       <c r="L91">
-        <f t="shared" si="38"/>
-        <v>100</v>
+        <f t="shared" si="9"/>
+        <v>20</v>
       </c>
       <c r="M91">
         <v>0</v>
@@ -5224,15 +5806,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A92">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="B92">
-        <v>1040</v>
+        <v>-1000</v>
       </c>
       <c r="C92">
-        <v>440</v>
+        <v>0</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -5244,48 +5826,48 @@
         <v>0</v>
       </c>
       <c r="G92">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H92">
         <v>1</v>
       </c>
       <c r="I92">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J92">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="K92">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L92">
-        <f t="shared" si="38"/>
-        <v>140</v>
+        <f t="shared" si="9"/>
+        <v>20</v>
       </c>
       <c r="M92">
-        <v>-120</v>
+        <v>0</v>
       </c>
       <c r="N92">
-        <v>1040</v>
+        <v>0</v>
       </c>
       <c r="O92">
-        <v>440</v>
+        <v>0</v>
       </c>
       <c r="P92">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A93">
-        <v>-120</v>
+        <v>0</v>
       </c>
       <c r="B93">
-        <v>1080</v>
+        <v>-1000</v>
       </c>
       <c r="C93">
-        <v>460</v>
+        <v>0</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -5297,48 +5879,48 @@
         <v>0</v>
       </c>
       <c r="G93">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H93">
         <v>1</v>
       </c>
       <c r="I93">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J93">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="K93">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L93">
-        <f t="shared" si="38"/>
-        <v>100</v>
+        <f t="shared" si="9"/>
+        <v>20</v>
       </c>
       <c r="M93">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="N93">
-        <v>1080</v>
+        <v>0</v>
       </c>
       <c r="O93">
-        <v>460</v>
+        <v>0</v>
       </c>
       <c r="P93">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A94">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="B94">
-        <v>1120</v>
+        <v>-1000</v>
       </c>
       <c r="C94">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -5350,48 +5932,48 @@
         <v>0</v>
       </c>
       <c r="G94">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H94">
         <v>1</v>
       </c>
       <c r="I94">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J94">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="K94">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L94">
-        <f t="shared" si="38"/>
-        <v>60</v>
+        <f t="shared" si="9"/>
+        <v>20</v>
       </c>
       <c r="M94">
-        <v>-120</v>
+        <v>0</v>
       </c>
       <c r="N94">
-        <v>1120</v>
+        <v>0</v>
       </c>
       <c r="O94">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="P94">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A95">
         <v>0</v>
       </c>
       <c r="B95">
-        <v>1140</v>
+        <v>-1000</v>
       </c>
       <c r="C95">
-        <v>640</v>
+        <v>0</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -5403,25 +5985,25 @@
         <v>0</v>
       </c>
       <c r="G95">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H95">
         <v>1</v>
       </c>
       <c r="I95">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J95">
-        <f t="shared" si="36"/>
-        <v>60</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="K95">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L95">
-        <f t="shared" si="38"/>
-        <v>60</v>
+        <f t="shared" si="9"/>
+        <v>20</v>
       </c>
       <c r="M95">
         <v>0</v>
@@ -5436,12 +6018,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A96">
         <v>0</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -5465,15 +6047,15 @@
         <v>1</v>
       </c>
       <c r="J96">
-        <f t="shared" si="36"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="K96">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L96">
-        <f t="shared" si="38"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="M96">
@@ -5489,21 +6071,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A97">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="B97">
-        <v>100</v>
+        <v>-1000</v>
       </c>
       <c r="C97">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
       <c r="E97">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -5518,15 +6100,15 @@
         <v>1</v>
       </c>
       <c r="J97">
-        <f t="shared" si="36"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="K97">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L97">
-        <f t="shared" si="38"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="M97">
@@ -5542,21 +6124,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A98">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="B98">
-        <v>280</v>
+        <v>-1000</v>
       </c>
       <c r="C98">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="D98">
         <v>0</v>
       </c>
       <c r="E98">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -5571,15 +6153,15 @@
         <v>1</v>
       </c>
       <c r="J98">
-        <f t="shared" si="36"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="K98">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L98">
-        <f t="shared" si="38"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="M98">
@@ -5595,15 +6177,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A99">
         <v>0</v>
       </c>
       <c r="B99">
-        <v>520</v>
+        <v>-1000</v>
       </c>
       <c r="C99">
-        <v>-340</v>
+        <v>0</v>
       </c>
       <c r="D99">
         <v>0</v>
@@ -5624,15 +6206,15 @@
         <v>1</v>
       </c>
       <c r="J99">
-        <f t="shared" si="36"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="K99">
-        <f t="shared" si="37"/>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L99">
-        <f t="shared" si="38"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="M99">
@@ -5648,61 +6230,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A100">
-        <v>0</v>
-      </c>
-      <c r="B100">
-        <v>1200</v>
-      </c>
-      <c r="C100">
-        <v>-1080</v>
-      </c>
-      <c r="D100">
-        <v>0</v>
-      </c>
-      <c r="E100">
-        <v>0</v>
-      </c>
-      <c r="F100">
-        <v>0</v>
-      </c>
-      <c r="G100">
-        <v>1</v>
-      </c>
-      <c r="H100">
-        <v>1</v>
-      </c>
-      <c r="I100">
-        <v>1</v>
-      </c>
-      <c r="J100">
-        <f t="shared" si="36"/>
-        <v>20</v>
-      </c>
-      <c r="K100">
-        <f t="shared" si="37"/>
-        <v>20</v>
-      </c>
-      <c r="L100">
-        <f t="shared" si="38"/>
-        <v>20</v>
-      </c>
-      <c r="M100">
-        <v>0</v>
-      </c>
-      <c r="N100">
-        <v>0</v>
-      </c>
-      <c r="O100">
-        <v>0</v>
-      </c>
-      <c r="P100">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
+  <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Action-敵追加中-/Data/CSV/Stage/Stage.xlsx
+++ b/Action-敵追加中-/Data/CSV/Stage/Stage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action-敵追加中-\Data\CSV\Stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action-敵追加中-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96B7F007-ABCC-40B3-B33F-0521BEB77628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{65EE512D-456A-4E3E-8689-6824860A0EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stage" sheetId="1" r:id="rId1"/>
@@ -681,9 +681,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -721,7 +721,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -827,7 +827,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -969,7 +969,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -977,7 +977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P99"/>
+  <dimension ref="A1:P98"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="16" width="5.625" customWidth="1"/>
@@ -1065,15 +1065,15 @@
         <v>21</v>
       </c>
       <c r="J2">
-        <f t="shared" ref="J2:J64" si="1">G2*20</f>
+        <f t="shared" ref="J2:J63" si="1">G2*20</f>
         <v>200</v>
       </c>
       <c r="K2">
-        <f t="shared" ref="K2:K64" si="2">H2*20</f>
+        <f t="shared" ref="K2:K63" si="2">H2*20</f>
         <v>20</v>
       </c>
       <c r="L2">
-        <f t="shared" ref="L2:L64" si="3">I2*20</f>
+        <f t="shared" ref="L2:L63" si="3">I2*20</f>
         <v>420</v>
       </c>
       <c r="M2">
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="B15">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C15">
         <v>-2660</v>
@@ -1745,17 +1745,17 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H15">
         <v>1</v>
       </c>
       <c r="I15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J15">
         <f t="shared" si="1"/>
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="K15">
         <f t="shared" si="2"/>
@@ -1763,16 +1763,16 @@
       </c>
       <c r="L15">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="M15">
         <v>0</v>
       </c>
       <c r="N15">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="O15">
-        <v>-2640</v>
+        <v>-2660</v>
       </c>
       <c r="P15">
         <v>1</v>
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="B16">
-        <v>-1000</v>
+        <v>300</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>-2920</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1798,17 +1798,17 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H16">
         <v>1</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="J16">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="K16">
         <f t="shared" si="2"/>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L16">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>420</v>
       </c>
       <c r="M16">
         <v>0</v>
@@ -1833,13 +1833,13 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A17">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="B17">
-        <v>-1000</v>
+        <v>300</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1851,17 +1851,17 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H17">
         <v>1</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J17">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>420</v>
       </c>
       <c r="K17">
         <f t="shared" si="2"/>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="L17">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -1886,13 +1886,13 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A18">
-        <v>0</v>
+        <v>730</v>
       </c>
       <c r="B18">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1904,17 +1904,17 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H18">
         <v>1</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J18">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>420</v>
       </c>
       <c r="K18">
         <f t="shared" si="2"/>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="L18">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -1939,13 +1939,13 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A19">
-        <v>0</v>
+        <v>1170</v>
       </c>
       <c r="B19">
-        <v>-1000</v>
+        <v>200</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1957,17 +1957,17 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H19">
         <v>1</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>420</v>
       </c>
       <c r="K19">
         <f t="shared" si="2"/>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="L19">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="M19">
         <v>0</v>
@@ -1992,13 +1992,13 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A20">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="B20">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>1</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I20">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J20">
         <f t="shared" si="1"/>
@@ -2024,11 +2024,11 @@
       </c>
       <c r="K20">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="L20">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="M20">
         <v>0</v>
@@ -2045,13 +2045,13 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A21">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="B21">
-        <v>-1000</v>
+        <v>200</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>-3095</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -2063,17 +2063,17 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H21">
         <v>1</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J21">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K21">
         <f t="shared" si="2"/>
@@ -2081,30 +2081,30 @@
       </c>
       <c r="L21">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>-3095</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A22">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="B22">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>-2965</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -2116,17 +2116,17 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H22">
         <v>1</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J22">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K22">
         <f t="shared" si="2"/>
@@ -2134,30 +2134,30 @@
       </c>
       <c r="L22">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>-2965</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A23">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="B23">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -2169,25 +2169,25 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J23">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K23">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="L23">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -2204,13 +2204,13 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A24">
-        <v>0</v>
+        <v>1390</v>
       </c>
       <c r="B24">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>1</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J24">
         <f t="shared" si="1"/>
@@ -2236,11 +2236,11 @@
       </c>
       <c r="K24">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="L24">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="M24">
         <v>0</v>
@@ -2257,13 +2257,13 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A25">
-        <v>0</v>
+        <v>1030</v>
       </c>
       <c r="B25">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -2281,7 +2281,7 @@
         <v>1</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J25">
         <f t="shared" si="1"/>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="L25">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M25">
         <v>0</v>
@@ -2310,13 +2310,13 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A26">
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="B26">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -2334,7 +2334,7 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J26">
         <f t="shared" si="1"/>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="L26">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M26">
         <v>0</v>
@@ -2363,13 +2363,14 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A27">
-        <v>0</v>
+        <f>A26+20</f>
+        <v>1070</v>
       </c>
       <c r="B27">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -2387,7 +2388,7 @@
         <v>1</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J27">
         <f t="shared" si="1"/>
@@ -2399,7 +2400,7 @@
       </c>
       <c r="L27">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -2416,13 +2417,14 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A28">
-        <v>0</v>
+        <f t="shared" ref="A28:A34" si="7">A27+20</f>
+        <v>1090</v>
       </c>
       <c r="B28">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -2440,7 +2442,7 @@
         <v>1</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J28">
         <f t="shared" si="1"/>
@@ -2452,7 +2454,7 @@
       </c>
       <c r="L28">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M28">
         <v>0</v>
@@ -2469,13 +2471,14 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A29">
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>1110</v>
       </c>
       <c r="B29">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -2493,7 +2496,7 @@
         <v>1</v>
       </c>
       <c r="I29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J29">
         <f t="shared" si="1"/>
@@ -2505,7 +2508,7 @@
       </c>
       <c r="L29">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M29">
         <v>0</v>
@@ -2522,13 +2525,14 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A30">
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>1130</v>
       </c>
       <c r="B30">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -2546,7 +2550,7 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J30">
         <f t="shared" si="1"/>
@@ -2558,7 +2562,7 @@
       </c>
       <c r="L30">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M30">
         <v>0</v>
@@ -2575,13 +2579,14 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A31">
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>1150</v>
       </c>
       <c r="B31">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -2599,7 +2604,7 @@
         <v>1</v>
       </c>
       <c r="I31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J31">
         <f t="shared" si="1"/>
@@ -2611,7 +2616,7 @@
       </c>
       <c r="L31">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M31">
         <v>0</v>
@@ -2628,13 +2633,14 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A32">
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>1170</v>
       </c>
       <c r="B32">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -2652,7 +2658,7 @@
         <v>1</v>
       </c>
       <c r="I32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J32">
         <f t="shared" si="1"/>
@@ -2664,7 +2670,7 @@
       </c>
       <c r="L32">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M32">
         <v>0</v>
@@ -2681,13 +2687,14 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A33">
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>1190</v>
       </c>
       <c r="B33">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -2705,7 +2712,7 @@
         <v>1</v>
       </c>
       <c r="I33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J33">
         <f t="shared" si="1"/>
@@ -2717,7 +2724,7 @@
       </c>
       <c r="L33">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M33">
         <v>0</v>
@@ -2734,13 +2741,14 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A34">
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>1210</v>
       </c>
       <c r="B34">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -2758,7 +2766,7 @@
         <v>1</v>
       </c>
       <c r="I34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J34">
         <f t="shared" si="1"/>
@@ -2770,7 +2778,7 @@
       </c>
       <c r="L34">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M34">
         <v>0</v>
@@ -2787,13 +2795,14 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A35">
-        <v>0</v>
+        <f t="shared" ref="A35:A39" si="8">A34+20</f>
+        <v>1230</v>
       </c>
       <c r="B35">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -2811,7 +2820,7 @@
         <v>1</v>
       </c>
       <c r="I35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J35">
         <f t="shared" si="1"/>
@@ -2823,7 +2832,7 @@
       </c>
       <c r="L35">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M35">
         <v>0</v>
@@ -2840,13 +2849,14 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A36">
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>1250</v>
       </c>
       <c r="B36">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -2864,7 +2874,7 @@
         <v>1</v>
       </c>
       <c r="I36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J36">
         <f t="shared" si="1"/>
@@ -2876,7 +2886,7 @@
       </c>
       <c r="L36">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -2893,13 +2903,14 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A37">
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>1270</v>
       </c>
       <c r="B37">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -2917,7 +2928,7 @@
         <v>1</v>
       </c>
       <c r="I37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J37">
         <f t="shared" si="1"/>
@@ -2929,7 +2940,7 @@
       </c>
       <c r="L37">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M37">
         <v>0</v>
@@ -2946,13 +2957,14 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A38">
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>1290</v>
       </c>
       <c r="B38">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2970,7 +2982,7 @@
         <v>1</v>
       </c>
       <c r="I38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J38">
         <f t="shared" si="1"/>
@@ -2982,7 +2994,7 @@
       </c>
       <c r="L38">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M38">
         <v>0</v>
@@ -2999,13 +3011,14 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A39">
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>1310</v>
       </c>
       <c r="B39">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -3023,7 +3036,7 @@
         <v>1</v>
       </c>
       <c r="I39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J39">
         <f t="shared" si="1"/>
@@ -3035,7 +3048,7 @@
       </c>
       <c r="L39">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M39">
         <v>0</v>
@@ -3052,13 +3065,14 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A40">
-        <v>0</v>
+        <f t="shared" ref="A40:A42" si="9">A39+20</f>
+        <v>1330</v>
       </c>
       <c r="B40">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -3076,7 +3090,7 @@
         <v>1</v>
       </c>
       <c r="I40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J40">
         <f t="shared" si="1"/>
@@ -3088,7 +3102,7 @@
       </c>
       <c r="L40">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M40">
         <v>0</v>
@@ -3105,13 +3119,14 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A41">
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>1350</v>
       </c>
       <c r="B41">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -3129,7 +3144,7 @@
         <v>1</v>
       </c>
       <c r="I41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J41">
         <f t="shared" si="1"/>
@@ -3141,7 +3156,7 @@
       </c>
       <c r="L41">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M41">
         <v>0</v>
@@ -3158,13 +3173,14 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A42">
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>1370</v>
       </c>
       <c r="B42">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -3182,7 +3198,7 @@
         <v>1</v>
       </c>
       <c r="I42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J42">
         <f t="shared" si="1"/>
@@ -3194,7 +3210,7 @@
       </c>
       <c r="L42">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M42">
         <v>0</v>
@@ -3211,13 +3227,13 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A43">
-        <v>0</v>
+        <v>1610</v>
       </c>
       <c r="B43">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -3229,17 +3245,17 @@
         <v>0</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H43">
         <v>1</v>
       </c>
       <c r="I43">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J43">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>420</v>
       </c>
       <c r="K43">
         <f t="shared" si="2"/>
@@ -3247,7 +3263,7 @@
       </c>
       <c r="L43">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="M43">
         <v>0</v>
@@ -4351,15 +4367,15 @@
         <v>1</v>
       </c>
       <c r="J64">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J64:J98" si="10">G64*20</f>
         <v>20</v>
       </c>
       <c r="K64">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="K64:K98" si="11">H64*20</f>
         <v>20</v>
       </c>
       <c r="L64">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="L64:L98" si="12">I64*20</f>
         <v>20</v>
       </c>
       <c r="M64">
@@ -4404,15 +4420,15 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <f t="shared" ref="J65:J99" si="7">G65*20</f>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K65">
-        <f t="shared" ref="K65:K99" si="8">H65*20</f>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L65">
-        <f t="shared" ref="L65:L99" si="9">I65*20</f>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M65">
@@ -4457,15 +4473,15 @@
         <v>1</v>
       </c>
       <c r="J66">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K66">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L66">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M66">
@@ -4510,15 +4526,15 @@
         <v>1</v>
       </c>
       <c r="J67">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K67">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L67">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M67">
@@ -4563,15 +4579,15 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K68">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L68">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M68">
@@ -4616,15 +4632,15 @@
         <v>1</v>
       </c>
       <c r="J69">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K69">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L69">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M69">
@@ -4669,15 +4685,15 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K70">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L70">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M70">
@@ -4722,15 +4738,15 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K71">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L71">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M71">
@@ -4775,15 +4791,15 @@
         <v>1</v>
       </c>
       <c r="J72">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K72">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L72">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M72">
@@ -4828,15 +4844,15 @@
         <v>1</v>
       </c>
       <c r="J73">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L73">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M73">
@@ -4881,15 +4897,15 @@
         <v>1</v>
       </c>
       <c r="J74">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K74">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L74">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M74">
@@ -4934,15 +4950,15 @@
         <v>1</v>
       </c>
       <c r="J75">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M75">
@@ -4987,15 +5003,15 @@
         <v>1</v>
       </c>
       <c r="J76">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K76">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L76">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M76">
@@ -5040,15 +5056,15 @@
         <v>1</v>
       </c>
       <c r="J77">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L77">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M77">
@@ -5093,15 +5109,15 @@
         <v>1</v>
       </c>
       <c r="J78">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K78">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L78">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M78">
@@ -5146,15 +5162,15 @@
         <v>1</v>
       </c>
       <c r="J79">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K79">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L79">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M79">
@@ -5199,15 +5215,15 @@
         <v>1</v>
       </c>
       <c r="J80">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K80">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L80">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M80">
@@ -5252,15 +5268,15 @@
         <v>1</v>
       </c>
       <c r="J81">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K81">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L81">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M81">
@@ -5305,15 +5321,15 @@
         <v>1</v>
       </c>
       <c r="J82">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K82">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L82">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M82">
@@ -5358,15 +5374,15 @@
         <v>1</v>
       </c>
       <c r="J83">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K83">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M83">
@@ -5411,15 +5427,15 @@
         <v>1</v>
       </c>
       <c r="J84">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K84">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L84">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M84">
@@ -5464,15 +5480,15 @@
         <v>1</v>
       </c>
       <c r="J85">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K85">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M85">
@@ -5517,15 +5533,15 @@
         <v>1</v>
       </c>
       <c r="J86">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K86">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L86">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M86">
@@ -5570,15 +5586,15 @@
         <v>1</v>
       </c>
       <c r="J87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K87">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L87">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M87">
@@ -5623,15 +5639,15 @@
         <v>1</v>
       </c>
       <c r="J88">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K88">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L88">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M88">
@@ -5676,15 +5692,15 @@
         <v>1</v>
       </c>
       <c r="J89">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K89">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L89">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M89">
@@ -5729,15 +5745,15 @@
         <v>1</v>
       </c>
       <c r="J90">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K90">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M90">
@@ -5782,15 +5798,15 @@
         <v>1</v>
       </c>
       <c r="J91">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K91">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L91">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M91">
@@ -5835,15 +5851,15 @@
         <v>1</v>
       </c>
       <c r="J92">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K92">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L92">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M92">
@@ -5888,15 +5904,15 @@
         <v>1</v>
       </c>
       <c r="J93">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K93">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L93">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M93">
@@ -5941,15 +5957,15 @@
         <v>1</v>
       </c>
       <c r="J94">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K94">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L94">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M94">
@@ -5994,15 +6010,15 @@
         <v>1</v>
       </c>
       <c r="J95">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K95">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L95">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M95">
@@ -6047,15 +6063,15 @@
         <v>1</v>
       </c>
       <c r="J96">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K96">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L96">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M96">
@@ -6100,15 +6116,15 @@
         <v>1</v>
       </c>
       <c r="J97">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K97">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L97">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M97">
@@ -6153,15 +6169,15 @@
         <v>1</v>
       </c>
       <c r="J98">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="K98">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="L98">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="M98">
@@ -6174,59 +6190,6 @@
         <v>0</v>
       </c>
       <c r="P98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A99">
-        <v>0</v>
-      </c>
-      <c r="B99">
-        <v>-1000</v>
-      </c>
-      <c r="C99">
-        <v>0</v>
-      </c>
-      <c r="D99">
-        <v>0</v>
-      </c>
-      <c r="E99">
-        <v>0</v>
-      </c>
-      <c r="F99">
-        <v>0</v>
-      </c>
-      <c r="G99">
-        <v>1</v>
-      </c>
-      <c r="H99">
-        <v>1</v>
-      </c>
-      <c r="I99">
-        <v>1</v>
-      </c>
-      <c r="J99">
-        <f t="shared" si="7"/>
-        <v>20</v>
-      </c>
-      <c r="K99">
-        <f t="shared" si="8"/>
-        <v>20</v>
-      </c>
-      <c r="L99">
-        <f t="shared" si="9"/>
-        <v>20</v>
-      </c>
-      <c r="M99">
-        <v>0</v>
-      </c>
-      <c r="N99">
-        <v>0</v>
-      </c>
-      <c r="O99">
-        <v>0</v>
-      </c>
-      <c r="P99">
         <v>0</v>
       </c>
     </row>

--- a/Action-敵追加中-/Data/CSV/Stage/Stage.xlsx
+++ b/Action-敵追加中-/Data/CSV/Stage/Stage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ita20\OneDrive\デスクトップ\GameProject\Action-敵追加中-\Data\CSV\Stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action-敵追加中-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65EE512D-456A-4E3E-8689-6824860A0EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{ED149A5A-C74F-4210-B9E0-7F118C4D308F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stage" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,10 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -681,9 +685,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -721,7 +725,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -827,7 +831,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -969,7 +973,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1939,7 +1943,7 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A19">
-        <v>1170</v>
+        <v>1090</v>
       </c>
       <c r="B19">
         <v>200</v>
@@ -1957,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -1967,7 +1971,7 @@
       </c>
       <c r="J19">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>300</v>
       </c>
       <c r="K19">
         <f t="shared" si="2"/>
@@ -2051,7 +2055,7 @@
         <v>200</v>
       </c>
       <c r="C21">
-        <v>-3095</v>
+        <v>-3100</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -2069,7 +2073,7 @@
         <v>1</v>
       </c>
       <c r="I21">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J21">
         <f t="shared" si="1"/>
@@ -2081,7 +2085,7 @@
       </c>
       <c r="L21">
         <f t="shared" si="3"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M21">
         <v>990</v>
@@ -2090,7 +2094,7 @@
         <v>320</v>
       </c>
       <c r="O21">
-        <v>-3095</v>
+        <v>-3100</v>
       </c>
       <c r="P21">
         <v>0.5</v>
@@ -2104,7 +2108,7 @@
         <v>320</v>
       </c>
       <c r="C22">
-        <v>-2965</v>
+        <v>-2960</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -2122,7 +2126,7 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J22">
         <f t="shared" si="1"/>
@@ -2134,7 +2138,7 @@
       </c>
       <c r="L22">
         <f t="shared" si="3"/>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M22">
         <v>990</v>
@@ -2143,7 +2147,7 @@
         <v>200</v>
       </c>
       <c r="O22">
-        <v>-2965</v>
+        <v>-2960</v>
       </c>
       <c r="P22">
         <v>0.5</v>
@@ -2175,7 +2179,7 @@
         <v>7</v>
       </c>
       <c r="I23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J23">
         <f t="shared" si="1"/>
@@ -2187,7 +2191,7 @@
       </c>
       <c r="L23">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -2204,7 +2208,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A24">
-        <v>1390</v>
+        <v>1230</v>
       </c>
       <c r="B24">
         <v>320</v>
@@ -2281,7 +2285,7 @@
         <v>1</v>
       </c>
       <c r="I25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J25">
         <f t="shared" si="1"/>
@@ -2293,7 +2297,7 @@
       </c>
       <c r="L25">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M25">
         <v>0</v>
@@ -2334,7 +2338,7 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J26">
         <f t="shared" si="1"/>
@@ -2346,7 +2350,7 @@
       </c>
       <c r="L26">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M26">
         <v>0</v>
@@ -2388,7 +2392,7 @@
         <v>1</v>
       </c>
       <c r="I27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27">
         <f t="shared" si="1"/>
@@ -2400,7 +2404,7 @@
       </c>
       <c r="L27">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -2442,7 +2446,7 @@
         <v>1</v>
       </c>
       <c r="I28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J28">
         <f t="shared" si="1"/>
@@ -2454,7 +2458,7 @@
       </c>
       <c r="L28">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M28">
         <v>0</v>
@@ -2496,7 +2500,7 @@
         <v>1</v>
       </c>
       <c r="I29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J29">
         <f t="shared" si="1"/>
@@ -2508,7 +2512,7 @@
       </c>
       <c r="L29">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M29">
         <v>0</v>
@@ -2550,7 +2554,7 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30">
         <f t="shared" si="1"/>
@@ -2562,7 +2566,7 @@
       </c>
       <c r="L30">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M30">
         <v>0</v>
@@ -2604,7 +2608,7 @@
         <v>1</v>
       </c>
       <c r="I31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J31">
         <f t="shared" si="1"/>
@@ -2616,7 +2620,7 @@
       </c>
       <c r="L31">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M31">
         <v>0</v>
@@ -2658,7 +2662,7 @@
         <v>1</v>
       </c>
       <c r="I32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J32">
         <f t="shared" si="1"/>
@@ -2670,7 +2674,7 @@
       </c>
       <c r="L32">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M32">
         <v>0</v>
@@ -2712,7 +2716,7 @@
         <v>1</v>
       </c>
       <c r="I33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J33">
         <f t="shared" si="1"/>
@@ -2724,7 +2728,7 @@
       </c>
       <c r="L33">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M33">
         <v>0</v>
@@ -2766,7 +2770,7 @@
         <v>1</v>
       </c>
       <c r="I34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J34">
         <f t="shared" si="1"/>
@@ -2778,7 +2782,7 @@
       </c>
       <c r="L34">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M34">
         <v>0</v>
@@ -2795,8 +2799,7 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A35">
-        <f t="shared" ref="A35:A39" si="8">A34+20</f>
-        <v>1230</v>
+        <v>1450</v>
       </c>
       <c r="B35">
         <v>320</v>
@@ -2814,25 +2817,25 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H35">
         <v>1</v>
       </c>
       <c r="I35">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J35">
-        <f t="shared" si="1"/>
-        <v>20</v>
+        <f t="shared" ref="J35:J36" si="8">G35*20</f>
+        <v>420</v>
       </c>
       <c r="K35">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="K35:K36" si="9">H35*20</f>
         <v>20</v>
       </c>
       <c r="L35">
-        <f t="shared" si="3"/>
-        <v>60</v>
+        <f t="shared" ref="L35:L36" si="10">I35*20</f>
+        <v>200</v>
       </c>
       <c r="M35">
         <v>0</v>
@@ -2849,44 +2852,43 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A36">
+        <v>0</v>
+      </c>
+      <c r="B36">
+        <v>-1000</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="J36">
         <f t="shared" si="8"/>
-        <v>1250</v>
-      </c>
-      <c r="B36">
-        <v>320</v>
-      </c>
-      <c r="C36">
-        <v>-3030</v>
-      </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36">
-        <v>0</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-      <c r="H36">
-        <v>1</v>
-      </c>
-      <c r="I36">
-        <v>3</v>
-      </c>
-      <c r="J36">
-        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="K36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="L36">
-        <f t="shared" si="3"/>
-        <v>60</v>
+        <f t="shared" si="10"/>
+        <v>20</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -2903,14 +2905,13 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A37">
-        <f t="shared" si="8"/>
-        <v>1270</v>
+        <v>0</v>
       </c>
       <c r="B37">
-        <v>320</v>
+        <v>-1000</v>
       </c>
       <c r="C37">
-        <v>-3030</v>
+        <v>0</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -2928,19 +2929,19 @@
         <v>1</v>
       </c>
       <c r="I37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J37">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J37:J43" si="11">G37*20</f>
         <v>20</v>
       </c>
       <c r="K37">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="K37:K43" si="12">H37*20</f>
         <v>20</v>
       </c>
       <c r="L37">
-        <f t="shared" si="3"/>
-        <v>60</v>
+        <f t="shared" ref="L37:L43" si="13">I37*20</f>
+        <v>20</v>
       </c>
       <c r="M37">
         <v>0</v>
@@ -2957,14 +2958,13 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A38">
-        <f t="shared" si="8"/>
-        <v>1290</v>
+        <v>0</v>
       </c>
       <c r="B38">
-        <v>320</v>
+        <v>-1000</v>
       </c>
       <c r="C38">
-        <v>-3030</v>
+        <v>0</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2982,19 +2982,19 @@
         <v>1</v>
       </c>
       <c r="I38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="K38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="L38">
-        <f t="shared" si="3"/>
-        <v>60</v>
+        <f t="shared" si="13"/>
+        <v>20</v>
       </c>
       <c r="M38">
         <v>0</v>
@@ -3011,14 +3011,13 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A39">
-        <f t="shared" si="8"/>
-        <v>1310</v>
+        <v>0</v>
       </c>
       <c r="B39">
-        <v>320</v>
+        <v>-1000</v>
       </c>
       <c r="C39">
-        <v>-3030</v>
+        <v>0</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -3036,19 +3035,19 @@
         <v>1</v>
       </c>
       <c r="I39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="K39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="L39">
-        <f t="shared" si="3"/>
-        <v>60</v>
+        <f t="shared" si="13"/>
+        <v>20</v>
       </c>
       <c r="M39">
         <v>0</v>
@@ -3065,14 +3064,13 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A40">
-        <f t="shared" ref="A40:A42" si="9">A39+20</f>
-        <v>1330</v>
+        <v>0</v>
       </c>
       <c r="B40">
-        <v>320</v>
+        <v>-1000</v>
       </c>
       <c r="C40">
-        <v>-3030</v>
+        <v>0</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -3090,19 +3088,19 @@
         <v>1</v>
       </c>
       <c r="I40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="K40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="L40">
-        <f t="shared" si="3"/>
-        <v>60</v>
+        <f t="shared" si="13"/>
+        <v>20</v>
       </c>
       <c r="M40">
         <v>0</v>
@@ -3119,14 +3117,13 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A41">
-        <f t="shared" si="9"/>
-        <v>1350</v>
+        <v>0</v>
       </c>
       <c r="B41">
-        <v>320</v>
+        <v>-1000</v>
       </c>
       <c r="C41">
-        <v>-3030</v>
+        <v>0</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -3144,19 +3141,19 @@
         <v>1</v>
       </c>
       <c r="I41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J41">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="K41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="L41">
-        <f t="shared" si="3"/>
-        <v>60</v>
+        <f t="shared" si="13"/>
+        <v>20</v>
       </c>
       <c r="M41">
         <v>0</v>
@@ -3173,14 +3170,13 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A42">
-        <f t="shared" si="9"/>
-        <v>1370</v>
+        <v>0</v>
       </c>
       <c r="B42">
-        <v>320</v>
+        <v>-1000</v>
       </c>
       <c r="C42">
-        <v>-3030</v>
+        <v>0</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -3198,19 +3194,19 @@
         <v>1</v>
       </c>
       <c r="I42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J42">
-        <f t="shared" si="1"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="K42">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="L42">
-        <f t="shared" si="3"/>
-        <v>60</v>
+        <f t="shared" si="13"/>
+        <v>20</v>
       </c>
       <c r="M42">
         <v>0</v>
@@ -3227,13 +3223,13 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A43">
-        <v>1610</v>
+        <v>0</v>
       </c>
       <c r="B43">
-        <v>320</v>
+        <v>-1000</v>
       </c>
       <c r="C43">
-        <v>-3030</v>
+        <v>0</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -3245,25 +3241,25 @@
         <v>0</v>
       </c>
       <c r="G43">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="H43">
         <v>1</v>
       </c>
       <c r="I43">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J43">
-        <f t="shared" si="1"/>
-        <v>420</v>
+        <f t="shared" si="11"/>
+        <v>20</v>
       </c>
       <c r="K43">
-        <f t="shared" si="2"/>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="L43">
-        <f t="shared" si="3"/>
-        <v>200</v>
+        <f t="shared" si="13"/>
+        <v>20</v>
       </c>
       <c r="M43">
         <v>0</v>
@@ -4367,15 +4363,15 @@
         <v>1</v>
       </c>
       <c r="J64">
-        <f t="shared" ref="J64:J98" si="10">G64*20</f>
+        <f t="shared" ref="J64:J98" si="14">G64*20</f>
         <v>20</v>
       </c>
       <c r="K64">
-        <f t="shared" ref="K64:K98" si="11">H64*20</f>
+        <f t="shared" ref="K64:K98" si="15">H64*20</f>
         <v>20</v>
       </c>
       <c r="L64">
-        <f t="shared" ref="L64:L98" si="12">I64*20</f>
+        <f t="shared" ref="L64:L98" si="16">I64*20</f>
         <v>20</v>
       </c>
       <c r="M64">
@@ -4420,15 +4416,15 @@
         <v>1</v>
       </c>
       <c r="J65">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K65">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L65">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M65">
@@ -4473,15 +4469,15 @@
         <v>1</v>
       </c>
       <c r="J66">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K66">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L66">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M66">
@@ -4526,15 +4522,15 @@
         <v>1</v>
       </c>
       <c r="J67">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K67">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L67">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M67">
@@ -4579,15 +4575,15 @@
         <v>1</v>
       </c>
       <c r="J68">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K68">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L68">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M68">
@@ -4632,15 +4628,15 @@
         <v>1</v>
       </c>
       <c r="J69">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K69">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L69">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M69">
@@ -4685,15 +4681,15 @@
         <v>1</v>
       </c>
       <c r="J70">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K70">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L70">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M70">
@@ -4738,15 +4734,15 @@
         <v>1</v>
       </c>
       <c r="J71">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K71">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L71">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M71">
@@ -4791,15 +4787,15 @@
         <v>1</v>
       </c>
       <c r="J72">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K72">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L72">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M72">
@@ -4844,15 +4840,15 @@
         <v>1</v>
       </c>
       <c r="J73">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K73">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L73">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M73">
@@ -4897,15 +4893,15 @@
         <v>1</v>
       </c>
       <c r="J74">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K74">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L74">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M74">
@@ -4950,15 +4946,15 @@
         <v>1</v>
       </c>
       <c r="J75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L75">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M75">
@@ -5003,15 +4999,15 @@
         <v>1</v>
       </c>
       <c r="J76">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K76">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L76">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M76">
@@ -5056,15 +5052,15 @@
         <v>1</v>
       </c>
       <c r="J77">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K77">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L77">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M77">
@@ -5109,15 +5105,15 @@
         <v>1</v>
       </c>
       <c r="J78">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K78">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L78">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M78">
@@ -5162,15 +5158,15 @@
         <v>1</v>
       </c>
       <c r="J79">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K79">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L79">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M79">
@@ -5215,15 +5211,15 @@
         <v>1</v>
       </c>
       <c r="J80">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K80">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L80">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M80">
@@ -5268,15 +5264,15 @@
         <v>1</v>
       </c>
       <c r="J81">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K81">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L81">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M81">
@@ -5321,15 +5317,15 @@
         <v>1</v>
       </c>
       <c r="J82">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K82">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L82">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M82">
@@ -5374,15 +5370,15 @@
         <v>1</v>
       </c>
       <c r="J83">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K83">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L83">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M83">
@@ -5427,15 +5423,15 @@
         <v>1</v>
       </c>
       <c r="J84">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K84">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L84">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M84">
@@ -5480,15 +5476,15 @@
         <v>1</v>
       </c>
       <c r="J85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K85">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L85">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M85">
@@ -5533,15 +5529,15 @@
         <v>1</v>
       </c>
       <c r="J86">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K86">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L86">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M86">
@@ -5586,15 +5582,15 @@
         <v>1</v>
       </c>
       <c r="J87">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L87">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M87">
@@ -5639,15 +5635,15 @@
         <v>1</v>
       </c>
       <c r="J88">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K88">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L88">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M88">
@@ -5692,15 +5688,15 @@
         <v>1</v>
       </c>
       <c r="J89">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K89">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L89">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M89">
@@ -5745,15 +5741,15 @@
         <v>1</v>
       </c>
       <c r="J90">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L90">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M90">
@@ -5798,15 +5794,15 @@
         <v>1</v>
       </c>
       <c r="J91">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K91">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L91">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M91">
@@ -5851,15 +5847,15 @@
         <v>1</v>
       </c>
       <c r="J92">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K92">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L92">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M92">
@@ -5904,15 +5900,15 @@
         <v>1</v>
       </c>
       <c r="J93">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K93">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L93">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M93">
@@ -5957,15 +5953,15 @@
         <v>1</v>
       </c>
       <c r="J94">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K94">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L94">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M94">
@@ -6010,15 +6006,15 @@
         <v>1</v>
       </c>
       <c r="J95">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K95">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L95">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M95">
@@ -6063,15 +6059,15 @@
         <v>1</v>
       </c>
       <c r="J96">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K96">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L96">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M96">
@@ -6116,15 +6112,15 @@
         <v>1</v>
       </c>
       <c r="J97">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K97">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L97">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M97">
@@ -6169,15 +6165,15 @@
         <v>1</v>
       </c>
       <c r="J98">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="K98">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>20</v>
       </c>
       <c r="L98">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="M98">

--- a/Action-敵追加中-/Data/CSV/Stage/Stage.xlsx
+++ b/Action-敵追加中-/Data/CSV/Stage/Stage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action-敵追加中-\Data\CSV\Stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\2409404\Desktop\GameProject\Action-敵追加中-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{ED149A5A-C74F-4210-B9E0-7F118C4D308F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{ECBAD746-DE3F-4AF5-B1B6-6D184BA5965A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stage" sheetId="1" r:id="rId1"/>
@@ -26,12 +26,11 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2852,13 +2851,13 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A36">
-        <v>0</v>
+        <v>1610</v>
       </c>
       <c r="B36">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>-3180</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -2870,17 +2869,17 @@
         <v>0</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H36">
         <v>1</v>
       </c>
       <c r="I36">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J36">
         <f t="shared" si="8"/>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K36">
         <f t="shared" si="9"/>
@@ -2888,30 +2887,31 @@
       </c>
       <c r="L36">
         <f t="shared" si="10"/>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>2610</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>-3180</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A37">
-        <v>0</v>
+        <v>2610</v>
       </c>
       <c r="B37">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <f>-2880</f>
+        <v>-2880</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -2923,17 +2923,17 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H37">
         <v>1</v>
       </c>
       <c r="I37">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J37">
         <f t="shared" ref="J37:J43" si="11">G37*20</f>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K37">
         <f t="shared" ref="K37:K43" si="12">H37*20</f>
@@ -2941,30 +2941,31 @@
       </c>
       <c r="L37">
         <f t="shared" ref="L37:L43" si="13">I37*20</f>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>1610</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <f>-2880</f>
+        <v>-2880</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A38">
-        <v>0</v>
+        <v>2770</v>
       </c>
       <c r="B38">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2976,17 +2977,17 @@
         <v>0</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H38">
         <v>1</v>
       </c>
       <c r="I38">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J38">
         <f t="shared" si="11"/>
-        <v>20</v>
+        <v>420</v>
       </c>
       <c r="K38">
         <f t="shared" si="12"/>
@@ -2994,7 +2995,7 @@
       </c>
       <c r="L38">
         <f t="shared" si="13"/>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="M38">
         <v>0</v>
@@ -3011,13 +3012,13 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A39">
-        <v>0</v>
+        <v>3480</v>
       </c>
       <c r="B39">
-        <v>-1000</v>
+        <v>340</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -3029,17 +3030,17 @@
         <v>0</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H39">
         <v>1</v>
       </c>
       <c r="I39">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="J39">
         <f t="shared" si="11"/>
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="K39">
         <f t="shared" si="12"/>
@@ -3047,7 +3048,7 @@
       </c>
       <c r="L39">
         <f t="shared" si="13"/>
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="M39">
         <v>0</v>
@@ -3064,13 +3065,13 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A40">
-        <v>0</v>
+        <v>4030</v>
       </c>
       <c r="B40">
-        <v>-1000</v>
+        <v>340</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -3082,17 +3083,17 @@
         <v>0</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H40">
         <v>1</v>
       </c>
       <c r="I40">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J40">
         <f t="shared" si="11"/>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K40">
         <f t="shared" si="12"/>
@@ -3100,7 +3101,7 @@
       </c>
       <c r="L40">
         <f t="shared" si="13"/>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="M40">
         <v>0</v>

--- a/Action-敵追加中-/Data/CSV/Stage/Stage.xlsx
+++ b/Action-敵追加中-/Data/CSV/Stage/Stage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\2409404\Desktop\GameProject\Action-敵追加中-\Data\CSV\Stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409404\Desktop\GameProject\Action-敵追加中-\Data\CSV\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{ECBAD746-DE3F-4AF5-B1B6-6D184BA5965A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC13A609-576A-49ED-817B-F653BC701F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stage" sheetId="1" r:id="rId1"/>
@@ -3118,19 +3118,19 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A41">
-        <v>0</v>
+        <v>4030</v>
       </c>
       <c r="B41">
-        <v>-1000</v>
+        <v>340</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -3174,10 +3174,10 @@
         <v>0</v>
       </c>
       <c r="B42">
-        <v>-1000</v>
+        <v>80</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>-1680</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -3198,8 +3198,7 @@
         <v>1</v>
       </c>
       <c r="J42">
-        <f t="shared" si="11"/>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="K42">
         <f t="shared" si="12"/>
@@ -3227,10 +3226,10 @@
         <v>0</v>
       </c>
       <c r="B43">
-        <v>-1000</v>
+        <v>300</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>-2920</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -3251,8 +3250,7 @@
         <v>1</v>
       </c>
       <c r="J43">
-        <f t="shared" si="11"/>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="K43">
         <f t="shared" si="12"/>
@@ -3277,19 +3275,19 @@
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A44">
-        <v>0</v>
+        <v>1450</v>
       </c>
       <c r="B44">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -3312,8 +3310,7 @@
         <v>20</v>
       </c>
       <c r="L44">
-        <f t="shared" si="3"/>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="M44">
         <v>0</v>
@@ -3330,19 +3327,19 @@
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A45">
-        <v>0</v>
+        <v>2770</v>
       </c>
       <c r="B45">
-        <v>-1000</v>
+        <v>320</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>-3030</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -3365,8 +3362,7 @@
         <v>20</v>
       </c>
       <c r="L45">
-        <f t="shared" si="3"/>
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="M45">
         <v>0</v>
